--- a/samples/conformance.xlsx
+++ b/samples/conformance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nyank\Desktop\後藤さんのclaude\ai-builders-2026\gridlint\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6FAA89C4-8A33-446D-AF7C-231B8157C201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{866E915D-E1E2-477B-B2E9-CC601363A0B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{123645F8-76AB-4974-974A-34148C5324E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F9E2885-0765-40A0-BA70-23B21BCC5425}"/>
   </bookViews>
   <sheets>
     <sheet name="Calc" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="177">
   <si>
     <t>text</t>
   </si>
@@ -91,6 +91,18 @@
     <t>huge</t>
   </si>
   <si>
+    <t>q1</t>
+  </si>
+  <si>
+    <t>q2</t>
+  </si>
+  <si>
+    <t>q3</t>
+  </si>
+  <si>
+    <t>q4</t>
+  </si>
+  <si>
     <t>case</t>
   </si>
   <si>
@@ -371,12 +383,205 @@
   </si>
   <si>
     <t>chain of refs</t>
+  </si>
+  <si>
+    <t>sumifs one condition</t>
+  </si>
+  <si>
+    <t>sumifs two conditions</t>
+  </si>
+  <si>
+    <t>sumifs no match</t>
+  </si>
+  <si>
+    <t>countifs one condition</t>
+  </si>
+  <si>
+    <t>countifs two conditions</t>
+  </si>
+  <si>
+    <t>countifs numeric range</t>
+  </si>
+  <si>
+    <t>averageifs</t>
+  </si>
+  <si>
+    <t>maxifs</t>
+  </si>
+  <si>
+    <t>minifs</t>
+  </si>
+  <si>
+    <t>sumproduct two arrays</t>
+  </si>
+  <si>
+    <t>sumproduct as a condition</t>
+  </si>
+  <si>
+    <t>sumproduct single array</t>
+  </si>
+  <si>
+    <t>ifs first match</t>
+  </si>
+  <si>
+    <t>ifs later match</t>
+  </si>
+  <si>
+    <t>switch matched</t>
+  </si>
+  <si>
+    <t>switch default</t>
+  </si>
+  <si>
+    <t>choose</t>
+  </si>
+  <si>
+    <t>xlookup exact</t>
+  </si>
+  <si>
+    <t>xlookup not found</t>
+  </si>
+  <si>
+    <t>xlookup next larger</t>
+  </si>
+  <si>
+    <t>hlookup exact</t>
+  </si>
+  <si>
+    <t>isna on lookup</t>
+  </si>
+  <si>
+    <t>na literal caught</t>
+  </si>
+  <si>
+    <t>date builds a serial</t>
+  </si>
+  <si>
+    <t>year month day</t>
+  </si>
+  <si>
+    <t>date arithmetic</t>
+  </si>
+  <si>
+    <t>eomonth this month</t>
+  </si>
+  <si>
+    <t>eomonth previous</t>
+  </si>
+  <si>
+    <t>edate plus three</t>
+  </si>
+  <si>
+    <t>days between</t>
+  </si>
+  <si>
+    <t>weekday default</t>
+  </si>
+  <si>
+    <t>weekday monday one</t>
+  </si>
+  <si>
+    <t>datedif months</t>
+  </si>
+  <si>
+    <t>date rolls month overflow</t>
+  </si>
+  <si>
+    <t>npv</t>
+  </si>
+  <si>
+    <t>npv plus initial</t>
+  </si>
+  <si>
+    <t>irr</t>
+  </si>
+  <si>
+    <t>pmt</t>
+  </si>
+  <si>
+    <t>pmt zero rate</t>
+  </si>
+  <si>
+    <t>pv</t>
+  </si>
+  <si>
+    <t>fv</t>
+  </si>
+  <si>
+    <t>mod positive</t>
+  </si>
+  <si>
+    <t>mod negative dividend</t>
+  </si>
+  <si>
+    <t>mod negative divisor</t>
+  </si>
+  <si>
+    <t>ceiling</t>
+  </si>
+  <si>
+    <t>ceiling exact</t>
+  </si>
+  <si>
+    <t>floor</t>
+  </si>
+  <si>
+    <t>sign</t>
+  </si>
+  <si>
+    <t>median odd</t>
+  </si>
+  <si>
+    <t>median even</t>
+  </si>
+  <si>
+    <t>stdev sample</t>
+  </si>
+  <si>
+    <t>large second</t>
+  </si>
+  <si>
+    <t>small second</t>
+  </si>
+  <si>
+    <t>textjoin skipping blanks</t>
+  </si>
+  <si>
+    <t>textjoin keeping blanks</t>
+  </si>
+  <si>
+    <t>substitute all</t>
+  </si>
+  <si>
+    <t>substitute nth</t>
+  </si>
+  <si>
+    <t>replace</t>
+  </si>
+  <si>
+    <t>find is case sensitive</t>
+  </si>
+  <si>
+    <t>search is not</t>
+  </si>
+  <si>
+    <t>proper</t>
+  </si>
+  <si>
+    <t>rept</t>
+  </si>
+  <si>
+    <t>len of joined</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="8" formatCode="&quot;¥&quot;#,##0.00;[Red]&quot;¥&quot;\-#,##0.00"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -416,8 +621,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -753,21 +967,36 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C85FE248-6B24-4BEB-B79F-67375165B773}">
-  <dimension ref="A1:L94"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AA93ED9-B30D-4138-9860-6FE5808B27FE}">
+  <dimension ref="A1:Q157"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="13" max="13" width="11.375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="O1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="P1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B2">
         <f>-2^2</f>
@@ -788,16 +1017,34 @@
       <c r="I2">
         <v>10</v>
       </c>
+      <c r="J2">
+        <v>-1000</v>
+      </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M2" s="1">
+        <v>46095.625</v>
+      </c>
+      <c r="N2">
+        <v>11</v>
+      </c>
+      <c r="O2">
+        <v>22</v>
+      </c>
+      <c r="P2">
+        <v>33</v>
+      </c>
+      <c r="Q2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B3">
         <f>2^3^2</f>
@@ -818,16 +1065,22 @@
       <c r="I3">
         <v>20</v>
       </c>
+      <c r="J3">
+        <v>250</v>
+      </c>
       <c r="K3">
         <v>10</v>
       </c>
       <c r="L3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="M3" s="1">
+        <v>46390.625</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B4">
         <f>50%*40</f>
@@ -848,6 +1101,9 @@
       <c r="I4">
         <v>30</v>
       </c>
+      <c r="J4">
+        <v>300</v>
+      </c>
       <c r="K4">
         <v>30</v>
       </c>
@@ -855,9 +1111,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B5">
         <f>(10+10)%</f>
@@ -875,6 +1131,9 @@
       <c r="I5">
         <v>40</v>
       </c>
+      <c r="J5">
+        <v>350</v>
+      </c>
       <c r="K5">
         <v>60</v>
       </c>
@@ -882,9 +1141,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B6">
         <f>2+3*4-6/3</f>
@@ -905,6 +1164,9 @@
       <c r="I6">
         <v>50</v>
       </c>
+      <c r="J6">
+        <v>400</v>
+      </c>
       <c r="K6">
         <v>100</v>
       </c>
@@ -912,9 +1174,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B7" t="b">
         <f>3&gt;2</f>
@@ -929,10 +1191,13 @@
       <c r="F7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="J7">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B8" t="b">
         <f>AND(3&gt;2,2&gt;1)</f>
@@ -948,9 +1213,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B9">
         <f>2^-2</f>
@@ -963,9 +1228,9 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B10">
         <f>((2+3)*(4-1))/5</f>
@@ -981,9 +1246,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B11">
         <f>--5</f>
@@ -999,45 +1264,45 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B12">
         <f>"7"+1</f>
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B13">
         <f>TRUE+1</f>
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B14">
         <f>Z100+5</f>
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B15" t="str">
         <f>Z100&amp;"x"</f>
         <v>x</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B16" t="str">
         <f>1/4&amp;""</f>
@@ -1046,7 +1311,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B17" t="str">
         <f>1234567&amp;""</f>
@@ -1055,7 +1320,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B18" t="b">
         <f>"abc"="ABC"</f>
@@ -1064,7 +1329,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B19" t="b">
         <f>("a"&gt;1)</f>
@@ -1073,7 +1338,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B20" t="b">
         <f>(TRUE&gt;"z")</f>
@@ -1082,7 +1347,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B21" t="e">
         <f>1/0</f>
@@ -1091,7 +1356,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B22" t="str">
         <f>IFERROR(1/0,"caught")</f>
@@ -1100,7 +1365,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B23">
         <f>IFERROR(6/2,0)</f>
@@ -1109,7 +1374,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B24" t="e">
         <f>SUM(1,1/0)</f>
@@ -1118,7 +1383,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B25" t="b">
         <f>ISERROR(1/0)</f>
@@ -1127,7 +1392,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B26" t="b">
         <f>ISERROR(1)</f>
@@ -1136,7 +1401,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B27" t="e">
         <f>1+"abc"</f>
@@ -1145,7 +1410,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B28">
         <f>IF(TRUE,1,1/0)</f>
@@ -1154,7 +1419,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B29" t="str">
         <f>IFERROR(#N/A,"na")</f>
@@ -1163,7 +1428,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B30">
         <f>ROUND(0.5,0)</f>
@@ -1172,7 +1437,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B31">
         <f>ROUND(-0.5,0)</f>
@@ -1181,7 +1446,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B32">
         <f>ROUND(2.5,0)</f>
@@ -1190,7 +1455,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B33">
         <f>ROUND(2.675,2)</f>
@@ -1199,7 +1464,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B34">
         <f>ROUND(12345,-2)</f>
@@ -1208,7 +1473,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B35">
         <f>ROUNDUP(2.001,2)</f>
@@ -1217,7 +1482,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B36">
         <f>ROUNDDOWN(2.999,2)</f>
@@ -1226,7 +1491,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B37">
         <f>INT(-2.1)</f>
@@ -1235,7 +1500,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B38">
         <f>ABS(-7.5)</f>
@@ -1244,7 +1509,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B39">
         <f>SQRT(16)</f>
@@ -1253,7 +1518,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B40">
         <f>POWER(3,4)</f>
@@ -1262,7 +1527,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B41">
         <f>SUM($E$2:$E$11)</f>
@@ -1271,7 +1536,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B42">
         <f>SUM($F$2:$F$11)</f>
@@ -1280,7 +1545,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B43">
         <f>SUM("3",4)</f>
@@ -1289,7 +1554,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B44">
         <f>AVERAGE($E$2:$E$11)</f>
@@ -1298,7 +1563,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B45">
         <f>AVERAGE($F$2:$F$11)</f>
@@ -1307,7 +1572,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B46">
         <f>MIN($E$2:$E$11)</f>
@@ -1316,7 +1581,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B47">
         <f>MAX($E$2:$E$11)</f>
@@ -1325,7 +1590,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B48">
         <f>COUNT($F$2:$F$11)</f>
@@ -1334,7 +1599,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B49">
         <f>COUNTA($F$2:$F$11)</f>
@@ -1343,7 +1608,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B50">
         <f>COUNTBLANK($F$2:$F$11)</f>
@@ -1352,7 +1617,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B51">
         <f>PRODUCT(2,3,4)</f>
@@ -1361,7 +1626,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B52">
         <f>SUM($Y$50:$Y$60)</f>
@@ -1370,7 +1635,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B53">
         <f>SUM(MAX($E$2:$E$11),MIN($E$2:$E$11))</f>
@@ -1379,7 +1644,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B54">
         <f>SUM($E$2:$E$5,100,$E$6)</f>
@@ -1388,7 +1653,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B55">
         <f>COUNTIF($E$2:$E$11,"&gt;50")</f>
@@ -1397,7 +1662,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B56">
         <f>COUNTIF($E$2:$E$11,40)</f>
@@ -1406,7 +1671,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B57">
         <f>COUNTIF($D$2:$D$11,"north")</f>
@@ -1415,7 +1680,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B58">
         <f>COUNTIF($D$2:$D$11,"&lt;&gt;north")</f>
@@ -1424,7 +1689,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B59">
         <f>COUNTIF($D$2:$D$11,"n*")</f>
@@ -1433,7 +1698,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B60">
         <f>SUMIF($D$2:$D$11,"north",$E$2:$E$11)</f>
@@ -1442,7 +1707,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B61">
         <f>SUMIF($E$2:$E$11,"&gt;50")</f>
@@ -1451,7 +1716,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B62">
         <f>SUMIF($D$2:$D$11,"south",$E$2:$E$11)</f>
@@ -1460,7 +1725,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B63">
         <f>AVERAGEIF($D$2:$D$11,"north",$E$2:$E$11)</f>
@@ -1469,7 +1734,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B64" t="str">
         <f>IF(1=1,"yes","no")</f>
@@ -1478,7 +1743,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B65" t="str">
         <f>IF(1=2,"yes","no")</f>
@@ -1487,7 +1752,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B66" t="str">
         <f>IF($E$2&gt;100,"big",IF($E$2&gt;10,"mid","small"))</f>
@@ -1496,7 +1761,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B67" t="b">
         <f>AND(OR(FALSE,TRUE),NOT(FALSE))</f>
@@ -1505,7 +1770,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B68">
         <f>IF(TRUE,42,0)</f>
@@ -1514,7 +1779,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B69" t="b">
         <f>ISBLANK($Z$100)</f>
@@ -1523,7 +1788,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B70" t="b">
         <f>ISNUMBER($E$2)</f>
@@ -1532,7 +1797,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B71" t="b">
         <f>ISTEXT($D$2)</f>
@@ -1541,7 +1806,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B72" t="str">
         <f>"a"&amp;"b"&amp;"c"</f>
@@ -1550,7 +1815,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B73" t="str">
         <f>CONCATENATE("x",1,"y")</f>
@@ -1559,7 +1824,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B74">
         <f>LEN("hello")</f>
@@ -1568,7 +1833,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B75" t="str">
         <f>LEFT("hello",3)</f>
@@ -1577,7 +1842,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B76" t="str">
         <f>RIGHT("hello",2)</f>
@@ -1595,7 +1860,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B78" t="str">
         <f>TRIM("  a   b  ")</f>
@@ -1604,7 +1869,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B79" t="str">
         <f>UPPER("ab")&amp;LOWER("CD")</f>
@@ -1613,7 +1878,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B80">
         <f>VALUE("12.5")+1</f>
@@ -1622,7 +1887,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B81" t="str">
         <f>TEXT(3.14159,"0.00")</f>
@@ -1631,7 +1896,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B82" t="str">
         <f>TEXT(0.1234,"0.0%")</f>
@@ -1640,7 +1905,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B83" t="str">
         <f>ROUND(1/3,4)&amp;" done"</f>
@@ -1649,7 +1914,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B84">
         <f>VLOOKUP("c",$H$2:$I$6,2,FALSE)</f>
@@ -1658,7 +1923,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B85" t="str">
         <f>VLOOKUP(35,$K$2:$L$6,2,TRUE)</f>
@@ -1667,7 +1932,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B86">
         <f>MATCH("c",$H$2:$H$6,0)</f>
@@ -1676,7 +1941,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B87">
         <f>INDEX($E$2:$E$11,3)</f>
@@ -1685,7 +1950,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B88">
         <f>INDEX($I$2:$I$6,MATCH("d",$H$2:$H$6,0))</f>
@@ -1694,7 +1959,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B89">
         <f>$E$2*2</f>
@@ -1703,7 +1968,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B90">
         <f>E$2+$E3</f>
@@ -1712,7 +1977,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B91">
         <f>Data!B2*10</f>
@@ -1721,7 +1986,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B92">
         <f>SUM(Data!B2:B5)</f>
@@ -1730,7 +1995,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B93">
         <f>'Odd Sheet'!B2+1</f>
@@ -1739,11 +2004,578 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B94">
         <f>B2+B3+B4</f>
         <v>88</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A95" t="s">
+        <v>114</v>
+      </c>
+      <c r="B95">
+        <f>SUMIFS($E$2:$E$11,$D$2:$D$11,"North")</f>
+        <v>315</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A96" t="s">
+        <v>115</v>
+      </c>
+      <c r="B96">
+        <f>SUMIFS($E$2:$E$11,$D$2:$D$11,"North",$E$2:$E$11,"&gt;50")</f>
+        <v>285</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A97" t="s">
+        <v>116</v>
+      </c>
+      <c r="B97">
+        <f>SUMIFS($E$2:$E$11,$D$2:$D$11,"Nowhere")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A98" t="s">
+        <v>117</v>
+      </c>
+      <c r="B98">
+        <f>COUNTIFS($D$2:$D$11,"South")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A99" t="s">
+        <v>118</v>
+      </c>
+      <c r="B99">
+        <f>COUNTIFS($D$2:$D$11,"North",$E$2:$E$11,"&lt;80")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A100" t="s">
+        <v>119</v>
+      </c>
+      <c r="B100">
+        <f>COUNTIFS($E$2:$E$11,"&gt;=40",$E$2:$E$11,"&lt;=90")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A101" t="s">
+        <v>120</v>
+      </c>
+      <c r="B101">
+        <f>AVERAGEIFS($E$2:$E$11,$D$2:$D$11,"North")</f>
+        <v>78.75</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A102" t="s">
+        <v>121</v>
+      </c>
+      <c r="B102">
+        <f>_xlfn.MAXIFS($E$2:$E$11,$D$2:$D$11,"South")</f>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A103" t="s">
+        <v>122</v>
+      </c>
+      <c r="B103">
+        <f>_xlfn.MINIFS($E$2:$E$11,$D$2:$D$11,"North")</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A104" t="s">
+        <v>123</v>
+      </c>
+      <c r="B104">
+        <f>SUMPRODUCT($E$2:$E$6,$I$2:$I$6)</f>
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A105" t="s">
+        <v>124</v>
+      </c>
+      <c r="B105">
+        <f>SUMPRODUCT(($D$2:$D$11="North")*$E$2:$E$11)</f>
+        <v>315</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A106" t="s">
+        <v>125</v>
+      </c>
+      <c r="B106">
+        <f>SUMPRODUCT($E$2:$E$11)</f>
+        <v>510</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A107" t="s">
+        <v>126</v>
+      </c>
+      <c r="B107" t="str">
+        <f>_xlfn.IFS($E$2&gt;100,"big",$E$2&gt;10,"mid",TRUE,"small")</f>
+        <v>big</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A108" t="s">
+        <v>127</v>
+      </c>
+      <c r="B108" t="str">
+        <f>_xlfn.IFS($E$3&gt;100,"big",$E$3&gt;10,"mid",TRUE,"small")</f>
+        <v>mid</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A109" t="s">
+        <v>128</v>
+      </c>
+      <c r="B109" t="str">
+        <f>_xlfn.SWITCH(2,1,"one",2,"two","other")</f>
+        <v>two</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A110" t="s">
+        <v>129</v>
+      </c>
+      <c r="B110" t="str">
+        <f>_xlfn.SWITCH(9,1,"one",2,"two","other")</f>
+        <v>other</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A111" t="s">
+        <v>130</v>
+      </c>
+      <c r="B111" t="str">
+        <f>CHOOSE(2,"a","b","c")</f>
+        <v>b</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A112" t="s">
+        <v>131</v>
+      </c>
+      <c r="B112">
+        <f>_xlfn.XLOOKUP("c",$H$2:$H$6,$I$2:$I$6)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A113" t="s">
+        <v>132</v>
+      </c>
+      <c r="B113" t="str">
+        <f>_xlfn.XLOOKUP("zz",$H$2:$H$6,$I$2:$I$6,"none")</f>
+        <v>none</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A114" t="s">
+        <v>133</v>
+      </c>
+      <c r="B114" t="str">
+        <f>_xlfn.XLOOKUP(35,$K$2:$K$6,$L$2:$L$6,"none",1)</f>
+        <v>large</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A115" t="s">
+        <v>134</v>
+      </c>
+      <c r="B115">
+        <f>HLOOKUP("q2",$N$1:$Q$2,2,FALSE)</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A116" t="s">
+        <v>135</v>
+      </c>
+      <c r="B116" t="b">
+        <f>ISNA(VLOOKUP("zz",$H$2:$I$6,2,FALSE))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A117" t="s">
+        <v>136</v>
+      </c>
+      <c r="B117">
+        <f>_xlfn.IFNA(NA(),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A118" t="s">
+        <v>137</v>
+      </c>
+      <c r="B118">
+        <f>DATE(2026,9,3)*1</f>
+        <v>46268</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A119" t="s">
+        <v>138</v>
+      </c>
+      <c r="B119">
+        <f>YEAR($M$2)*10000+MONTH($M$2)*100+DAY($M$2)</f>
+        <v>20260314</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A120" t="s">
+        <v>139</v>
+      </c>
+      <c r="B120">
+        <f>$M$3-$M$2</f>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A121" t="s">
+        <v>140</v>
+      </c>
+      <c r="B121" s="1">
+        <f>EOMONTH($M$2,0)-$M$2</f>
+        <v>16.375</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A122" t="s">
+        <v>141</v>
+      </c>
+      <c r="B122">
+        <f>EOMONTH($M$2,-1)*1</f>
+        <v>46081</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A123" t="s">
+        <v>142</v>
+      </c>
+      <c r="B123">
+        <f>EDATE($M$2,3)*1</f>
+        <v>46187</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A124" t="s">
+        <v>143</v>
+      </c>
+      <c r="B124">
+        <f>_xlfn.DAYS($M$3,$M$2)</f>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A125" t="s">
+        <v>144</v>
+      </c>
+      <c r="B125">
+        <f>WEEKDAY($M$2)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A126" t="s">
+        <v>145</v>
+      </c>
+      <c r="B126">
+        <f>WEEKDAY($M$2,2)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A127" t="s">
+        <v>146</v>
+      </c>
+      <c r="B127">
+        <f>DATEDIF($M$2,$M$3,"m")</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A128" t="s">
+        <v>147</v>
+      </c>
+      <c r="B128">
+        <f>DATE(2026,14,1)*1</f>
+        <v>46419</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A129" t="s">
+        <v>148</v>
+      </c>
+      <c r="B129" s="2">
+        <f>ROUND(NPV(0.1,$E$2:$E$6),6)</f>
+        <v>239.47817800000001</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A130" t="s">
+        <v>149</v>
+      </c>
+      <c r="B130" s="2">
+        <f>ROUND(NPV(0.08,$E$2:$E$6)-1000,6)</f>
+        <v>-750.27554399999997</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A131" t="s">
+        <v>150</v>
+      </c>
+      <c r="B131" s="3">
+        <f>ROUND(IRR($J$2:$J$7),6)</f>
+        <v>0.19711100000000001</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A132" t="s">
+        <v>151</v>
+      </c>
+      <c r="B132" s="2">
+        <f>ROUND(PMT(0.05/12,360,-300000),6)</f>
+        <v>1610.4648689999999</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A133" t="s">
+        <v>152</v>
+      </c>
+      <c r="B133" s="2">
+        <f>ROUND(PMT(0,120,-12000),6)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A134" t="s">
+        <v>153</v>
+      </c>
+      <c r="B134" s="2">
+        <f>ROUND(PV(0.06/12,120,-500),6)</f>
+        <v>45036.726664000002</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A135" t="s">
+        <v>154</v>
+      </c>
+      <c r="B135" s="2">
+        <f>ROUND(FV(0.06/12,120,-500),6)</f>
+        <v>81939.673402999993</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A136" t="s">
+        <v>155</v>
+      </c>
+      <c r="B136">
+        <f>MOD(17,5)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A137" t="s">
+        <v>156</v>
+      </c>
+      <c r="B137">
+        <f>MOD(-17,5)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A138" t="s">
+        <v>157</v>
+      </c>
+      <c r="B138">
+        <f>MOD(17,-5)</f>
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A139" t="s">
+        <v>158</v>
+      </c>
+      <c r="B139">
+        <f>CEILING(23,10)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A140" t="s">
+        <v>159</v>
+      </c>
+      <c r="B140">
+        <f>CEILING(20,10)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A141" t="s">
+        <v>160</v>
+      </c>
+      <c r="B141">
+        <f>FLOOR(27,10)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A142" t="s">
+        <v>161</v>
+      </c>
+      <c r="B142">
+        <f>SIGN(-4)+SIGN(0)+SIGN(9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A143" t="s">
+        <v>162</v>
+      </c>
+      <c r="B143">
+        <f>MEDIAN($E$2:$E$10)</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A144" t="s">
+        <v>163</v>
+      </c>
+      <c r="B144">
+        <f>MEDIAN($E$2:$E$11)</f>
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A145" t="s">
+        <v>164</v>
+      </c>
+      <c r="B145">
+        <f>ROUND(STDEV($E$2:$E$11),6)</f>
+        <v>37.103459000000001</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A146" t="s">
+        <v>165</v>
+      </c>
+      <c r="B146">
+        <f>LARGE($E$2:$E$11,2)</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A147" t="s">
+        <v>166</v>
+      </c>
+      <c r="B147">
+        <f>SMALL($E$2:$E$11,2)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A148" t="s">
+        <v>167</v>
+      </c>
+      <c r="B148" t="str">
+        <f>_xlfn.TEXTJOIN("-",TRUE,$H$2:$H$6)</f>
+        <v>a-b-c-d-e</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A149" t="s">
+        <v>168</v>
+      </c>
+      <c r="B149" t="str">
+        <f>_xlfn.TEXTJOIN("-",FALSE,$D$2:$D$4)</f>
+        <v>North-South-North</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A150" t="s">
+        <v>169</v>
+      </c>
+      <c r="B150" t="str">
+        <f>SUBSTITUTE("a-b-a","a","X")</f>
+        <v>X-b-X</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A151" t="s">
+        <v>170</v>
+      </c>
+      <c r="B151" t="str">
+        <f>SUBSTITUTE("a-b-a","a","X",2)</f>
+        <v>a-b-X</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A152" t="s">
+        <v>171</v>
+      </c>
+      <c r="B152" t="str">
+        <f>REPLACE("abcdef",2,3,"ZZ")</f>
+        <v>aZZef</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A153" t="s">
+        <v>172</v>
+      </c>
+      <c r="B153">
+        <f>FIND("B","aBcB")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A154" t="s">
+        <v>173</v>
+      </c>
+      <c r="B154">
+        <f>SEARCH("b","aBcB")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A155" t="s">
+        <v>174</v>
+      </c>
+      <c r="B155" t="str">
+        <f>PROPER("hello world")</f>
+        <v>Hello World</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A156" t="s">
+        <v>175</v>
+      </c>
+      <c r="B156" t="str">
+        <f>REPT("ab",3)</f>
+        <v>ababab</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A157" t="s">
+        <v>176</v>
+      </c>
+      <c r="B157">
+        <f>LEN(_xlfn.TEXTJOIN(",",TRUE,$H$2:$H$6))</f>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1753,7 +2585,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2F03B0D-5F53-4DD2-992D-E546D40722EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{721E6D8E-F901-4CC2-B432-1EF36805D4EC}">
   <dimension ref="B2:B5"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1784,7 +2616,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDD136F0-D5D1-450E-AFBA-493CE4734FB6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B4AC5C1-2F09-4364-9CBE-47FF91A55785}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
